--- a/ISTP to SPASE 2.x mapping.xlsx
+++ b/ISTP to SPASE 2.x mapping.xlsx
@@ -14,12 +14,21 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={4a6514d2-3de6-48fa-b94b-76981286bb5b}</author>
-    <author>tc={4b6c9aad-e3d5-4dbb-8726-94c44516de4c}</author>
-    <author>tc={540bb70b-a63a-456e-9c89-5c40ea1eca1a}</author>
+    <author>tc={115bc79f-1c28-43bb-9f20-91b3f6e0f9ac}</author>
+    <author>tc={9408b8c0-01cd-476d-a4fb-05b107ffbe10}</author>
+    <author>tc={f0934d39-d094-467e-ae06-7c4ab828bc87}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{4a6514d2-3de6-48fa-b94b-76981286bb5b}" ref="A54">
+    <comment authorId="0" xr:uid="{115bc79f-1c28-43bb-9f20-91b3f6e0f9ac}" ref="G30">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Update - Don't include because none have a clean mapping to a xsd:duration required by SPASE: https://hapi-server.org/meta/cdaweb/dataset/data/?_return=Time_resolution&amp;_uniques=true. Instead use computed cadence if available.
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{9408b8c0-01cd-476d-a4fb-05b107ffbe10}" ref="A55">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -28,16 +37,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{4b6c9aad-e3d5-4dbb-8726-94c44516de4c}" ref="G30">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Update - Don't include because none have a clean mapping to a xsd:duration required by SPASE: https://hapi-server.org/meta/cdaweb/dataset/data/?_return=Time_resolution&amp;_uniques=true. Instead use computed cadence if available.
-</t>
-      </text>
-    </comment>
-    <comment authorId="2" xr:uid="{540bb70b-a63a-456e-9c89-5c40ea1eca1a}" ref="B11">
+    <comment authorId="2" xr:uid="{f0934d39-d094-467e-ae06-7c4ab828bc87}" ref="B11">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="298">
   <si>
     <t>ISTP display types</t>
   </si>
@@ -98,9 +98,6 @@
     <t>list</t>
   </si>
   <si>
-    <t>SPASE paper (Table B.x)</t>
-  </si>
-  <si>
     <t>fuv_movie</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t>TimeSeries</t>
+  </si>
+  <si>
+    <t>SPASE paper (Table B.x)</t>
   </si>
   <si>
     <t>spectrogram</t>
@@ -158,6 +158,9 @@
     <t>map_movie</t>
   </si>
   <si>
+    <t>FINAL</t>
+  </si>
+  <si>
     <t>movie</t>
   </si>
   <si>
@@ -171,9 +174,6 @@
   </si>
   <si>
     <t>default_dimension</t>
-  </si>
-  <si>
-    <t>FINAL</t>
   </si>
   <si>
     <t>subject_category</t>
@@ -830,15 +830,6 @@
     <t>VALUEs in "Qualifier:VALUE[_VALUE...]" pair when DICT_KEY starts with "SPASE&gt;Field&gt;"</t>
   </si>
   <si>
-    <t>Parameter/Particle/ParticleType</t>
-  </si>
-  <si>
-    <t>ParticleType</t>
-  </si>
-  <si>
-    <t>VALUEs in "ParticleType:VALUE[_VALUE...]" pair when DICT_KEY starts with "SPASE&gt;Particle&gt;"</t>
-  </si>
-  <si>
     <t>Parameter/Particle/ParticleQuantity</t>
   </si>
   <si>
@@ -861,6 +852,15 @@
   </si>
   <si>
     <t>VALUEs in "AtomicNumber:VALUE[_VALUE...]" pair when DICT_KEY starts with "SPASE&gt;Particle&gt;"</t>
+  </si>
+  <si>
+    <t>Parameter/Particle/ParticleType</t>
+  </si>
+  <si>
+    <t>ParticleType</t>
+  </si>
+  <si>
+    <t>VALUE in "ParticleType:VALUE" pair when DICT_KEY starts with "SPASE&gt;Particle&gt;"</t>
   </si>
   <si>
     <t>Parameter/Wave/WaveType</t>
@@ -1205,7 +1205,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1457,6 +1457,9 @@
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -1482,8 +1485,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Rebecca Ringuette" id="{b6ad2461-0280-4d66-a478-0306b2feb66d}" providerId="google-sheets"/>
-  <x18tc:person displayName="Robert Weigel" id="{30ecfd1b-35f6-4847-befd-bf5e66c14428}" providerId="google-sheets"/>
+  <x18tc:person displayName="Rebecca Ringuette" id="{b296a393-05fc-4d2f-bdee-4b2e7a1b7807}" providerId="google-sheets"/>
+  <x18tc:person displayName="Robert Weigel" id="{7f6d98d1-5ff4-4433-8c55-105247ad287b}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1683,7 +1686,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G30" dT="2026-08-05T20:33:40.00" personId="{30ecfd1b-35f6-4847-befd-bf5e66c14428}" id="{4b6c9aad-e3d5-4dbb-8726-94c44516de4c}" done="0">
+  <x18tc:threadedComment ref="G30" dT="2026-08-05T20:33:40.00" personId="{7f6d98d1-5ff4-4433-8c55-105247ad287b}" id="{115bc79f-1c28-43bb-9f20-91b3f6e0f9ac}" done="0">
     <x18tc:text xml:space="preserve">Update - Don't include because none have a clean mapping to a xsd:duration required by SPASE: https://hapi-server.org/meta/cdaweb/dataset/data/?_return=Time_resolution&amp;_uniques=true. Instead use computed cadence if available.</x18tc:text>
     <x18tc:extLst>
       <ext uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
@@ -1692,10 +1695,10 @@
       </ext>
     </x18tc:extLst>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A54" dT="2026-08-04T22:18:57.00" personId="{b6ad2461-0280-4d66-a478-0306b2feb66d}" id="{4a6514d2-3de6-48fa-b94b-76981286bb5b}" done="0">
+  <x18tc:threadedComment ref="A55" dT="2026-08-04T22:18:57.00" personId="{b296a393-05fc-4d2f-bdee-4b2e7a1b7807}" id="{9408b8c0-01cd-476d-a4fb-05b107ffbe10}" done="0">
     <x18tc:text xml:space="preserve">These few red items are already accounted for by the block immediately following.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B11" dT="2026-05-06T17:49:13.00" personId="{b6ad2461-0280-4d66-a478-0306b2feb66d}" id="{540bb70b-a63a-456e-9c89-5c40ea1eca1a}" done="0">
+  <x18tc:threadedComment ref="B11" dT="2026-05-06T17:49:13.00" personId="{b296a393-05fc-4d2f-bdee-4b2e7a1b7807}" id="{f0934d39-d094-467e-ae06-7c4ab828bc87}" done="0">
     <x18tc:text xml:space="preserve">needs more details from Andriy</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1712,15 +1715,15 @@
     <col customWidth="1" min="2" max="2" width="18.13"/>
     <col customWidth="1" min="3" max="3" width="21.88"/>
     <col hidden="1" min="4" max="4" width="12.63"/>
-    <col customWidth="1" min="5" max="5" width="34.75"/>
-    <col customWidth="1" min="6" max="6" width="19.5"/>
-    <col customWidth="1" min="7" max="7" width="21.75"/>
-    <col customWidth="1" min="8" max="8" width="34.88"/>
-    <col customWidth="1" min="9" max="9" width="21.25"/>
-    <col customWidth="1" min="10" max="10" width="23.88"/>
-    <col customWidth="1" min="11" max="11" width="34.5"/>
-    <col customWidth="1" min="12" max="12" width="20.88"/>
-    <col customWidth="1" min="13" max="13" width="18.75"/>
+    <col customWidth="1" hidden="1" min="5" max="5" width="34.75"/>
+    <col customWidth="1" hidden="1" min="6" max="6" width="19.5"/>
+    <col customWidth="1" hidden="1" min="7" max="7" width="21.75"/>
+    <col customWidth="1" hidden="1" min="8" max="8" width="34.88"/>
+    <col customWidth="1" hidden="1" min="9" max="9" width="21.25"/>
+    <col customWidth="1" hidden="1" min="10" max="10" width="23.88"/>
+    <col customWidth="1" hidden="1" min="11" max="11" width="34.5"/>
+    <col customWidth="1" hidden="1" min="12" max="12" width="20.88"/>
+    <col customWidth="1" hidden="1" min="13" max="13" width="18.75"/>
     <col customWidth="1" min="14" max="14" width="0.88"/>
     <col customWidth="1" min="15" max="15" width="39.5"/>
     <col customWidth="1" min="16" max="16" width="26.88"/>
@@ -1752,7 +1755,7 @@
         <v>6</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M1" s="14"/>
       <c r="N1" s="15"/>
@@ -1760,7 +1763,7 @@
         <v>6</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
@@ -2570,7 +2573,7 @@
       <c r="J20" s="52"/>
       <c r="K20" s="53"/>
       <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
+      <c r="M20" s="14"/>
       <c r="N20" s="33"/>
       <c r="O20" s="50" t="s">
         <v>100</v>
@@ -3138,35 +3141,23 @@
       <c r="AB31" s="14"/>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
       <c r="D32" s="36"/>
-      <c r="E32" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="H32" s="14"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="14"/>
       <c r="J32" s="38"/>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="33"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q32" s="35" t="s">
-        <v>143</v>
-      </c>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="14"/>
       <c r="R32" s="14"/>
       <c r="S32" s="14"/>
       <c r="T32" s="14"/>
@@ -3180,95 +3171,87 @@
       <c r="AB32" s="14"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="F33" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="J33" s="38"/>
-      <c r="K33" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="L33" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="M33" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="N33" s="54"/>
-      <c r="O33" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="P33" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
+      <c r="A33" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="47"/>
+      <c r="N33" s="47"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q33" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="R33" s="47"/>
+      <c r="S33" s="47"/>
+      <c r="T33" s="47"/>
+      <c r="U33" s="47"/>
+      <c r="V33" s="47"/>
+      <c r="W33" s="47"/>
+      <c r="X33" s="47"/>
+      <c r="Y33" s="47"/>
+      <c r="Z33" s="47"/>
+      <c r="AA33" s="47"/>
+      <c r="AB33" s="47"/>
     </row>
     <row r="34">
       <c r="A34" s="37" t="s">
         <v>144</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="36"/>
       <c r="E34" s="35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="J34" s="38"/>
       <c r="K34" s="35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="L34" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="M34" s="14"/>
+        <v>76</v>
+      </c>
+      <c r="M34" s="35" t="s">
+        <v>147</v>
+      </c>
       <c r="N34" s="54"/>
       <c r="O34" s="35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P34" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q34" s="14"/>
+        <v>76</v>
+      </c>
+      <c r="Q34" s="35"/>
       <c r="R34" s="14"/>
       <c r="S34" s="14"/>
       <c r="T34" s="14"/>
@@ -3286,35 +3269,37 @@
         <v>144</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C35" s="35"/>
       <c r="D35" s="36"/>
       <c r="E35" s="35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>153</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G35" s="38"/>
       <c r="H35" s="35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="J35" s="38"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="K35" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="L35" s="35" t="s">
+        <v>150</v>
+      </c>
       <c r="M35" s="14"/>
-      <c r="N35" s="33"/>
+      <c r="N35" s="54"/>
       <c r="O35" s="35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P35" s="35" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="Q35" s="14"/>
       <c r="R35" s="14"/>
@@ -3334,7 +3319,7 @@
         <v>144</v>
       </c>
       <c r="B36" s="35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C36" s="35"/>
       <c r="D36" s="36"/>
@@ -3345,34 +3330,26 @@
         <v>72</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="J36" s="38"/>
-      <c r="K36" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="L36" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="M36" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="N36" s="54"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="33"/>
       <c r="O36" s="35" t="s">
         <v>152</v>
       </c>
       <c r="P36" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="Q36" s="35" t="s">
-        <v>157</v>
-      </c>
+      <c r="Q36" s="14"/>
       <c r="R36" s="14"/>
       <c r="S36" s="14"/>
       <c r="T36" s="14"/>
@@ -3390,43 +3367,45 @@
         <v>144</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C37" s="35"/>
       <c r="D37" s="36"/>
       <c r="E37" s="35" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="J37" s="38"/>
       <c r="K37" s="35" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L37" s="35" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="N37" s="54"/>
       <c r="O37" s="35" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="P37" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q37" s="35"/>
+        <v>72</v>
+      </c>
+      <c r="Q37" s="35" t="s">
+        <v>157</v>
+      </c>
       <c r="R37" s="14"/>
       <c r="S37" s="14"/>
       <c r="T37" s="14"/>
@@ -3440,192 +3419,196 @@
       <c r="AB37" s="14"/>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="s">
+      <c r="A38" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="35"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="H38" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="I38" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="J38" s="38"/>
+      <c r="K38" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="L38" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="M38" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="N38" s="54"/>
+      <c r="O38" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="P38" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="39" t="s">
+      <c r="C39" s="40"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
-      <c r="M38" s="40"/>
-      <c r="N38" s="54"/>
-      <c r="O38" s="40" t="s">
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="P38" s="40" t="s">
+      <c r="P39" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="Q38" s="40" t="s">
+      <c r="Q39" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="R38" s="42"/>
-      <c r="S38" s="42"/>
-      <c r="T38" s="42"/>
-      <c r="U38" s="42"/>
-      <c r="V38" s="42"/>
-      <c r="W38" s="42"/>
-      <c r="X38" s="42"/>
-      <c r="Y38" s="42"/>
-      <c r="Z38" s="42"/>
-      <c r="AA38" s="42"/>
-      <c r="AB38" s="42"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="37" t="s">
+      <c r="R39" s="42"/>
+      <c r="S39" s="42"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="42"/>
+      <c r="V39" s="42"/>
+      <c r="W39" s="42"/>
+      <c r="X39" s="42"/>
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="35" t="s">
+      <c r="B40" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="35" t="s">
+      <c r="C40" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="35" t="s">
+      <c r="D40" s="36"/>
+      <c r="E40" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="34" t="s">
+      <c r="F40" s="14"/>
+      <c r="G40" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H40" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="I39" s="35" t="s">
+      <c r="I40" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="J39" s="38"/>
-      <c r="K39" s="35" t="s">
+      <c r="J40" s="38"/>
+      <c r="K40" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="L39" s="35" t="s">
+      <c r="L40" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="M40" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="35" t="s">
+      <c r="N40" s="54"/>
+      <c r="O40" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="P39" s="35" t="s">
+      <c r="P40" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="14"/>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="I40" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="J40" s="43"/>
-      <c r="K40" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="L40" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="M40" s="42"/>
-      <c r="N40" s="54"/>
-      <c r="O40" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="P40" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q40" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="R40" s="42"/>
-      <c r="S40" s="42"/>
-      <c r="T40" s="42"/>
-      <c r="U40" s="42"/>
-      <c r="V40" s="42"/>
-      <c r="W40" s="42"/>
-      <c r="X40" s="42"/>
-      <c r="Y40" s="42"/>
-      <c r="Z40" s="42"/>
-      <c r="AA40" s="42"/>
-      <c r="AB40" s="42"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="14"/>
+      <c r="AA40" s="14"/>
+      <c r="AB40" s="14"/>
     </row>
     <row r="41">
       <c r="A41" s="39" t="s">
         <v>144</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C41" s="40"/>
+        <v>173</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>174</v>
+      </c>
       <c r="D41" s="41"/>
-      <c r="E41" s="42"/>
+      <c r="E41" s="40" t="s">
+        <v>175</v>
+      </c>
       <c r="F41" s="42"/>
       <c r="G41" s="39" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J41" s="43"/>
       <c r="K41" s="40" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="L41" s="40" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M41" s="42"/>
       <c r="N41" s="54"/>
       <c r="O41" s="40" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P41" s="40" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="Q41" s="40" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="R41" s="42"/>
       <c r="S41" s="42"/>
@@ -3644,7 +3627,7 @@
         <v>144</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C42" s="40"/>
       <c r="D42" s="41"/>
@@ -3654,10 +3637,10 @@
         <v>180</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J42" s="43"/>
       <c r="K42" s="40" t="s">
@@ -3669,12 +3652,14 @@
       <c r="M42" s="42"/>
       <c r="N42" s="54"/>
       <c r="O42" s="40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P42" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q42" s="42"/>
+        <v>182</v>
+      </c>
+      <c r="Q42" s="40" t="s">
+        <v>183</v>
+      </c>
       <c r="R42" s="42"/>
       <c r="S42" s="42"/>
       <c r="T42" s="42"/>
@@ -3688,67 +3673,63 @@
       <c r="AB42" s="42"/>
     </row>
     <row r="43">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="C43" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="D43" s="51"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="49" t="s">
+      <c r="B43" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="H43" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="I43" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="J43" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="K43" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="L43" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="M43" s="53"/>
+      <c r="H43" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="J43" s="43"/>
+      <c r="K43" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="L43" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="M43" s="42"/>
       <c r="N43" s="54"/>
-      <c r="O43" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="P43" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q43" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="53"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="53"/>
-      <c r="AB43" s="53"/>
-    </row>
-    <row r="44">
+      <c r="O43" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="P43" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="42"/>
+      <c r="V43" s="42"/>
+      <c r="W43" s="42"/>
+      <c r="X43" s="42"/>
+      <c r="Y43" s="42"/>
+      <c r="Z43" s="42"/>
+      <c r="AA43" s="42"/>
+      <c r="AB43" s="42"/>
+    </row>
+    <row r="44" hidden="1">
       <c r="A44" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B44" s="50" t="s">
-        <v>193</v>
-      </c>
-      <c r="C44" s="50"/>
+        <v>187</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>188</v>
+      </c>
       <c r="D44" s="51"/>
       <c r="E44" s="53"/>
       <c r="F44" s="53"/>
@@ -3756,24 +3737,30 @@
         <v>180</v>
       </c>
       <c r="H44" s="50" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I44" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="J44" s="52"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
+        <v>190</v>
+      </c>
+      <c r="J44" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="K44" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="L44" s="50" t="s">
+        <v>190</v>
+      </c>
       <c r="M44" s="53"/>
-      <c r="N44" s="33"/>
+      <c r="N44" s="54"/>
       <c r="O44" s="50" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="P44" s="50" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q44" s="50" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="R44" s="53"/>
       <c r="S44" s="53"/>
@@ -3787,31 +3774,37 @@
       <c r="AA44" s="53"/>
       <c r="AB44" s="53"/>
     </row>
-    <row r="45">
+    <row r="45" hidden="1">
       <c r="A45" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B45" s="50" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C45" s="50"/>
       <c r="D45" s="51"/>
       <c r="E45" s="53"/>
       <c r="F45" s="53"/>
       <c r="G45" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="H45" s="50"/>
-      <c r="I45" s="50"/>
+        <v>180</v>
+      </c>
+      <c r="H45" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="I45" s="50" t="s">
+        <v>195</v>
+      </c>
       <c r="J45" s="52"/>
       <c r="K45" s="53"/>
       <c r="L45" s="53"/>
       <c r="M45" s="53"/>
       <c r="N45" s="33"/>
       <c r="O45" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="P45" s="53"/>
+        <v>194</v>
+      </c>
+      <c r="P45" s="50" t="s">
+        <v>195</v>
+      </c>
       <c r="Q45" s="50" t="s">
         <v>196</v>
       </c>
@@ -3827,41 +3820,31 @@
       <c r="AA45" s="53"/>
       <c r="AB45" s="53"/>
     </row>
-    <row r="46">
+    <row r="46" hidden="1">
       <c r="A46" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B46" s="50" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C46" s="50"/>
       <c r="D46" s="51"/>
       <c r="E46" s="53"/>
       <c r="F46" s="53"/>
       <c r="G46" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="H46" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="I46" s="50" t="s">
-        <v>202</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H46" s="50"/>
+      <c r="I46" s="50"/>
       <c r="J46" s="52"/>
-      <c r="K46" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="L46" s="50" t="s">
-        <v>202</v>
-      </c>
+      <c r="K46" s="53"/>
+      <c r="L46" s="53"/>
       <c r="M46" s="53"/>
-      <c r="N46" s="54"/>
+      <c r="N46" s="33"/>
       <c r="O46" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="P46" s="50" t="s">
-        <v>202</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="P46" s="53"/>
       <c r="Q46" s="50" t="s">
         <v>196</v>
       </c>
@@ -3877,28 +3860,44 @@
       <c r="AA46" s="53"/>
       <c r="AB46" s="53"/>
     </row>
-    <row r="47">
+    <row r="47" hidden="1">
       <c r="A47" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B47" s="50" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C47" s="50"/>
       <c r="D47" s="51"/>
       <c r="E47" s="53"/>
       <c r="F47" s="53"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="50"/>
-      <c r="I47" s="50"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="50"/>
+      <c r="G47" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="H47" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="J47" s="52"/>
+      <c r="K47" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="L47" s="50" t="s">
+        <v>202</v>
+      </c>
       <c r="M47" s="53"/>
       <c r="N47" s="54"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="53"/>
+      <c r="O47" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="P47" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q47" s="50" t="s">
+        <v>196</v>
+      </c>
       <c r="R47" s="53"/>
       <c r="S47" s="53"/>
       <c r="T47" s="53"/>
@@ -3911,46 +3910,28 @@
       <c r="AA47" s="53"/>
       <c r="AB47" s="53"/>
     </row>
-    <row r="48">
+    <row r="48" hidden="1">
       <c r="A48" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B48" s="50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C48" s="50"/>
       <c r="D48" s="51"/>
       <c r="E48" s="53"/>
       <c r="F48" s="53"/>
-      <c r="G48" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="H48" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="I48" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="J48" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="K48" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="L48" s="50" t="s">
-        <v>206</v>
-      </c>
+      <c r="G48" s="49"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="50"/>
+      <c r="L48" s="50"/>
       <c r="M48" s="53"/>
       <c r="N48" s="54"/>
-      <c r="O48" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="P48" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q48" s="50" t="s">
-        <v>208</v>
-      </c>
+      <c r="O48" s="50"/>
+      <c r="P48" s="50"/>
+      <c r="Q48" s="53"/>
       <c r="R48" s="53"/>
       <c r="S48" s="53"/>
       <c r="T48" s="53"/>
@@ -3963,12 +3944,12 @@
       <c r="AA48" s="53"/>
       <c r="AB48" s="53"/>
     </row>
-    <row r="49">
+    <row r="49" hidden="1">
       <c r="A49" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B49" s="50" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C49" s="50"/>
       <c r="D49" s="51"/>
@@ -3977,25 +3958,31 @@
       <c r="G49" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="H49" s="50"/>
-      <c r="I49" s="50"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="56" t="s">
-        <v>210</v>
+      <c r="H49" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="I49" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="J49" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="K49" s="50" t="s">
+        <v>205</v>
       </c>
       <c r="L49" s="50" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="M49" s="53"/>
-      <c r="N49" s="57"/>
-      <c r="O49" s="56" t="s">
-        <v>210</v>
+      <c r="N49" s="54"/>
+      <c r="O49" s="50" t="s">
+        <v>205</v>
       </c>
       <c r="P49" s="50" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Q49" s="50" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="R49" s="53"/>
       <c r="S49" s="53"/>
@@ -4009,12 +3996,12 @@
       <c r="AA49" s="53"/>
       <c r="AB49" s="53"/>
     </row>
-    <row r="50">
+    <row r="50" hidden="1">
       <c r="A50" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B50" s="50" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C50" s="50"/>
       <c r="D50" s="51"/>
@@ -4026,19 +4013,19 @@
       <c r="H50" s="50"/>
       <c r="I50" s="50"/>
       <c r="J50" s="50"/>
-      <c r="K50" s="50" t="s">
-        <v>213</v>
+      <c r="K50" s="56" t="s">
+        <v>210</v>
       </c>
       <c r="L50" s="50" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M50" s="53"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="50" t="s">
-        <v>213</v>
+      <c r="N50" s="57"/>
+      <c r="O50" s="56" t="s">
+        <v>210</v>
       </c>
       <c r="P50" s="50" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q50" s="50" t="s">
         <v>196</v>
@@ -4055,34 +4042,36 @@
       <c r="AA50" s="53"/>
       <c r="AB50" s="53"/>
     </row>
-    <row r="51">
+    <row r="51" hidden="1">
       <c r="A51" s="49" t="s">
         <v>144</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C51" s="50"/>
       <c r="D51" s="51"/>
       <c r="E51" s="53"/>
       <c r="F51" s="53"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="52"/>
+      <c r="G51" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" s="50"/>
+      <c r="I51" s="50"/>
+      <c r="J51" s="50"/>
       <c r="K51" s="50" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L51" s="50" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M51" s="53"/>
       <c r="N51" s="54"/>
       <c r="O51" s="50" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P51" s="50" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q51" s="50" t="s">
         <v>196</v>
@@ -4099,65 +4088,63 @@
       <c r="AA51" s="53"/>
       <c r="AB51" s="53"/>
     </row>
-    <row r="52">
-      <c r="A52" s="37" t="s">
+    <row r="52" hidden="1">
+      <c r="A52" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="B52" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="L52" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="M52" s="35" t="s">
-        <v>162</v>
-      </c>
+      <c r="B52" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C52" s="50"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="L52" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="M52" s="53"/>
       <c r="N52" s="54"/>
-      <c r="O52" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="P52" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q52" s="35"/>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
-      <c r="T52" s="14"/>
-      <c r="U52" s="14"/>
-      <c r="V52" s="14"/>
-      <c r="W52" s="14"/>
-      <c r="X52" s="14"/>
-      <c r="Y52" s="14"/>
-      <c r="Z52" s="14"/>
-      <c r="AA52" s="14"/>
-      <c r="AB52" s="14"/>
+      <c r="O52" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="P52" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q52" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="R52" s="53"/>
+      <c r="S52" s="53"/>
+      <c r="T52" s="53"/>
+      <c r="U52" s="53"/>
+      <c r="V52" s="53"/>
+      <c r="W52" s="53"/>
+      <c r="X52" s="53"/>
+      <c r="Y52" s="53"/>
+      <c r="Z52" s="53"/>
+      <c r="AA52" s="53"/>
+      <c r="AB52" s="53"/>
     </row>
     <row r="53">
       <c r="A53" s="37" t="s">
         <v>144</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C53" s="35"/>
       <c r="D53" s="36"/>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
       <c r="G53" s="37" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
@@ -4169,7 +4156,7 @@
         <v>121</v>
       </c>
       <c r="M53" s="35" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="N53" s="54"/>
       <c r="O53" s="35" t="s">
@@ -4192,130 +4179,128 @@
       <c r="AB53" s="14"/>
     </row>
     <row r="54">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C54" s="35"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="L54" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="M54" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="N54" s="54"/>
+      <c r="O54" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="P54" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="14"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
+      <c r="Y54" s="14"/>
+      <c r="Z54" s="14"/>
+      <c r="AA54" s="14"/>
+      <c r="AB54" s="14"/>
+    </row>
+    <row r="55" hidden="1">
+      <c r="A55" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="C54" s="58"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="59" t="s">
+      <c r="C55" s="58"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="50" t="s">
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="50" t="s">
         <v>225</v>
       </c>
-      <c r="L54" s="50" t="s">
+      <c r="L55" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="M54" s="56" t="s">
+      <c r="M55" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="N54" s="54"/>
-      <c r="O54" s="50"/>
-      <c r="P54" s="50"/>
-      <c r="Q54" s="53"/>
-      <c r="R54" s="53"/>
-      <c r="S54" s="53"/>
-      <c r="T54" s="53"/>
-      <c r="U54" s="53"/>
-      <c r="V54" s="53"/>
-      <c r="W54" s="53"/>
-      <c r="X54" s="53"/>
-      <c r="Y54" s="53"/>
-      <c r="Z54" s="53"/>
-      <c r="AA54" s="53"/>
-      <c r="AB54" s="53"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="37" t="s">
+      <c r="N55" s="54"/>
+      <c r="O55" s="50"/>
+      <c r="P55" s="50"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="53"/>
+      <c r="S55" s="53"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="53"/>
+      <c r="W55" s="53"/>
+      <c r="X55" s="53"/>
+      <c r="Y55" s="53"/>
+      <c r="Z55" s="53"/>
+      <c r="AA55" s="53"/>
+      <c r="AB55" s="53"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="35" t="s">
+      <c r="B56" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="35"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="37" t="s">
+      <c r="C56" s="35"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="35" t="s">
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="L55" s="35" t="s">
+      <c r="L56" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M56" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="N55" s="54"/>
-      <c r="O55" s="35" t="s">
+      <c r="N56" s="54"/>
+      <c r="O56" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="P55" s="35" t="s">
+      <c r="P56" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="Q55" s="35" t="s">
+      <c r="Q56" s="35" t="s">
         <v>230</v>
-      </c>
-      <c r="R55" s="14"/>
-      <c r="S55" s="14"/>
-      <c r="T55" s="14"/>
-      <c r="U55" s="14"/>
-      <c r="V55" s="14"/>
-      <c r="W55" s="14"/>
-      <c r="X55" s="14"/>
-      <c r="Y55" s="14"/>
-      <c r="Z55" s="14"/>
-      <c r="AA55" s="14"/>
-      <c r="AB55" s="14"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B56" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="C56" s="61"/>
-      <c r="D56" s="62"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="60" t="s">
-        <v>232</v>
-      </c>
-      <c r="H56" s="63"/>
-      <c r="I56" s="63"/>
-      <c r="J56" s="64"/>
-      <c r="K56" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="L56" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="M56" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="N56" s="54"/>
-      <c r="O56" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="P56" s="61" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q56" s="61" t="s">
-        <v>233</v>
       </c>
       <c r="R56" s="14"/>
       <c r="S56" s="14"/>
@@ -4330,33 +4315,40 @@
       <c r="AB56" s="14"/>
     </row>
     <row r="57">
-      <c r="A57" s="37" t="s">
+      <c r="A57" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B57" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="C57" s="35"/>
-      <c r="D57" s="36"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="35"/>
+      <c r="B57" s="61" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="61"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="64"/>
+      <c r="K57" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="L57" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="M57" s="65" t="s">
+        <v>227</v>
+      </c>
       <c r="N57" s="54"/>
-      <c r="O57" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="P57" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q57" s="35" t="s">
-        <v>234</v>
+      <c r="O57" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="P57" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q57" s="61" t="s">
+        <v>233</v>
       </c>
       <c r="R57" s="14"/>
       <c r="S57" s="14"/>
@@ -4371,34 +4363,33 @@
       <c r="AB57" s="14"/>
     </row>
     <row r="58">
-      <c r="A58" s="60" t="s">
+      <c r="A58" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B58" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="C58" s="61"/>
-      <c r="D58" s="62"/>
-      <c r="E58" s="63"/>
-      <c r="F58" s="63"/>
-      <c r="G58" s="60" t="s">
-        <v>232</v>
-      </c>
-      <c r="H58" s="63"/>
-      <c r="I58" s="63"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="61"/>
-      <c r="L58" s="61"/>
-      <c r="M58" s="65"/>
+      <c r="B58" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58" s="35"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
       <c r="N58" s="54"/>
-      <c r="O58" s="61" t="s">
+      <c r="O58" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="P58" s="61" t="s">
+      <c r="P58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="Q58" s="61" t="s">
-        <v>235</v>
+      <c r="Q58" s="35" t="s">
+        <v>234</v>
       </c>
       <c r="R58" s="14"/>
       <c r="S58" s="14"/>
@@ -4413,130 +4404,124 @@
       <c r="AB58" s="14"/>
     </row>
     <row r="59">
-      <c r="A59" s="49" t="s">
+      <c r="A59" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="58" t="s">
+      <c r="B59" s="61" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59" s="61"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="64"/>
+      <c r="K59" s="61"/>
+      <c r="L59" s="61"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="54"/>
+      <c r="O59" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="P59" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q59" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="14"/>
+      <c r="V59" s="14"/>
+      <c r="W59" s="14"/>
+      <c r="X59" s="14"/>
+      <c r="Y59" s="14"/>
+      <c r="Z59" s="14"/>
+      <c r="AA59" s="14"/>
+      <c r="AB59" s="14"/>
+    </row>
+    <row r="60" hidden="1">
+      <c r="A60" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="C59" s="58"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="49" t="s">
+      <c r="C60" s="58"/>
+      <c r="D60" s="51"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="H59" s="53"/>
-      <c r="I59" s="53"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="50" t="s">
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="L59" s="50" t="s">
+      <c r="L60" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="M59" s="56" t="s">
+      <c r="M60" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="N59" s="54"/>
-      <c r="O59" s="50"/>
-      <c r="P59" s="50"/>
-      <c r="Q59" s="53"/>
-      <c r="R59" s="53"/>
-      <c r="S59" s="53"/>
-      <c r="T59" s="53"/>
-      <c r="U59" s="53"/>
-      <c r="V59" s="53"/>
-      <c r="W59" s="53"/>
-      <c r="X59" s="53"/>
-      <c r="Y59" s="53"/>
-      <c r="Z59" s="53"/>
-      <c r="AA59" s="53"/>
-      <c r="AB59" s="53"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="37" t="s">
+      <c r="N60" s="54"/>
+      <c r="O60" s="50"/>
+      <c r="P60" s="50"/>
+      <c r="Q60" s="53"/>
+      <c r="R60" s="53"/>
+      <c r="S60" s="53"/>
+      <c r="T60" s="53"/>
+      <c r="U60" s="53"/>
+      <c r="V60" s="53"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="53"/>
+      <c r="Y60" s="53"/>
+      <c r="Z60" s="53"/>
+      <c r="AA60" s="53"/>
+      <c r="AB60" s="53"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B61" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="C60" s="35"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="37" t="s">
+      <c r="C61" s="35"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="35" t="s">
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="L60" s="35" t="s">
+      <c r="L61" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="M60" s="10" t="s">
+      <c r="M61" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="N60" s="54"/>
-      <c r="O60" s="35" t="s">
+      <c r="N61" s="54"/>
+      <c r="O61" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="P60" s="35" t="s">
+      <c r="P61" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="Q60" s="35" t="s">
+      <c r="Q61" s="35" t="s">
         <v>238</v>
-      </c>
-      <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-      <c r="T60" s="14"/>
-      <c r="U60" s="14"/>
-      <c r="V60" s="14"/>
-      <c r="W60" s="14"/>
-      <c r="X60" s="14"/>
-      <c r="Y60" s="14"/>
-      <c r="Z60" s="14"/>
-      <c r="AA60" s="14"/>
-      <c r="AB60" s="14"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="B61" s="61" t="s">
-        <v>239</v>
-      </c>
-      <c r="C61" s="61"/>
-      <c r="D61" s="62"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="60" t="s">
-        <v>229</v>
-      </c>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="64"/>
-      <c r="K61" s="61" t="s">
-        <v>236</v>
-      </c>
-      <c r="L61" s="61" t="s">
-        <v>237</v>
-      </c>
-      <c r="M61" s="65" t="s">
-        <v>222</v>
-      </c>
-      <c r="N61" s="54"/>
-      <c r="O61" s="61" t="s">
-        <v>236</v>
-      </c>
-      <c r="P61" s="61" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q61" s="61" t="s">
-        <v>240</v>
       </c>
       <c r="R61" s="14"/>
       <c r="S61" s="14"/>
@@ -4551,33 +4536,40 @@
       <c r="AB61" s="14"/>
     </row>
     <row r="62">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="C62" s="35"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="37" t="s">
+      <c r="B62" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="C62" s="61"/>
+      <c r="D62" s="62"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="60" t="s">
         <v>229</v>
       </c>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="64"/>
+      <c r="K62" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="L62" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="M62" s="65" t="s">
+        <v>222</v>
+      </c>
       <c r="N62" s="54"/>
-      <c r="O62" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="P62" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q62" s="35" t="s">
-        <v>234</v>
+      <c r="O62" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="P62" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q62" s="61" t="s">
+        <v>240</v>
       </c>
       <c r="R62" s="14"/>
       <c r="S62" s="14"/>
@@ -4592,34 +4584,33 @@
       <c r="AB62" s="14"/>
     </row>
     <row r="63">
-      <c r="A63" s="60" t="s">
+      <c r="A63" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="B63" s="61" t="s">
-        <v>239</v>
-      </c>
-      <c r="C63" s="61"/>
-      <c r="D63" s="62"/>
-      <c r="E63" s="63"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="60" t="s">
+      <c r="B63" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C63" s="35"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="H63" s="63"/>
-      <c r="I63" s="63"/>
-      <c r="J63" s="64"/>
-      <c r="K63" s="61"/>
-      <c r="L63" s="61"/>
-      <c r="M63" s="65"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
       <c r="N63" s="54"/>
-      <c r="O63" s="61" t="s">
+      <c r="O63" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="P63" s="61" t="s">
+      <c r="P63" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="Q63" s="61" t="s">
-        <v>241</v>
+      <c r="Q63" s="35" t="s">
+        <v>234</v>
       </c>
       <c r="R63" s="14"/>
       <c r="S63" s="14"/>
@@ -4634,80 +4625,80 @@
       <c r="AB63" s="14"/>
     </row>
     <row r="64">
-      <c r="A64" s="66" t="s">
+      <c r="A64" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="61"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="60" t="s">
+        <v>229</v>
+      </c>
+      <c r="H64" s="63"/>
+      <c r="I64" s="63"/>
+      <c r="J64" s="64"/>
+      <c r="K64" s="61"/>
+      <c r="L64" s="61"/>
+      <c r="M64" s="65"/>
+      <c r="N64" s="54"/>
+      <c r="O64" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="P64" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q64" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+      <c r="Z64" s="14"/>
+      <c r="AA64" s="14"/>
+      <c r="AB64" s="14"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="70"/>
-      <c r="F64" s="70"/>
-      <c r="G64" s="71" t="s">
+      <c r="B65" s="67"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="H64" s="70"/>
-      <c r="I64" s="70"/>
-      <c r="J64" s="72"/>
-      <c r="K64" s="70"/>
-      <c r="L64" s="70"/>
-      <c r="M64" s="70"/>
-      <c r="N64" s="33"/>
-      <c r="O64" s="66"/>
-      <c r="P64" s="66"/>
-      <c r="Q64" s="73"/>
-      <c r="R64" s="70"/>
-      <c r="S64" s="70"/>
-      <c r="T64" s="70"/>
-      <c r="U64" s="70"/>
-      <c r="V64" s="70"/>
-      <c r="W64" s="70"/>
-      <c r="X64" s="70"/>
-      <c r="Y64" s="70"/>
-      <c r="Z64" s="70"/>
-      <c r="AA64" s="70"/>
-      <c r="AB64" s="70"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="B65" s="74" t="s">
-        <v>223</v>
-      </c>
-      <c r="C65" s="74"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
+      <c r="H65" s="70"/>
+      <c r="I65" s="70"/>
+      <c r="J65" s="72"/>
+      <c r="K65" s="70"/>
+      <c r="L65" s="70"/>
+      <c r="M65" s="70"/>
       <c r="N65" s="33"/>
-      <c r="O65" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="P65" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q65" s="75" t="s">
-        <v>245</v>
-      </c>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
-      <c r="T65" s="14"/>
-      <c r="U65" s="14"/>
-      <c r="V65" s="14"/>
-      <c r="W65" s="14"/>
-      <c r="X65" s="14"/>
-      <c r="Y65" s="14"/>
-      <c r="Z65" s="14"/>
-      <c r="AA65" s="14"/>
-      <c r="AB65" s="14"/>
+      <c r="O65" s="66"/>
+      <c r="P65" s="66"/>
+      <c r="Q65" s="73"/>
+      <c r="R65" s="70"/>
+      <c r="S65" s="70"/>
+      <c r="T65" s="70"/>
+      <c r="U65" s="70"/>
+      <c r="V65" s="70"/>
+      <c r="W65" s="70"/>
+      <c r="X65" s="70"/>
+      <c r="Y65" s="70"/>
+      <c r="Z65" s="70"/>
+      <c r="AA65" s="70"/>
+      <c r="AB65" s="70"/>
     </row>
     <row r="66">
       <c r="A66" s="37" t="s">
@@ -4731,13 +4722,13 @@
       <c r="M66" s="14"/>
       <c r="N66" s="33"/>
       <c r="O66" s="35" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="P66" s="35" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q66" s="75" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
@@ -4773,13 +4764,13 @@
       <c r="M67" s="14"/>
       <c r="N67" s="33"/>
       <c r="O67" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P67" s="35" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q67" s="75" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="14"/>
@@ -4815,13 +4806,13 @@
       <c r="M68" s="14"/>
       <c r="N68" s="33"/>
       <c r="O68" s="35" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P68" s="35" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q68" s="75" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="R68" s="14"/>
       <c r="S68" s="14"/>
@@ -4857,13 +4848,13 @@
       <c r="M69" s="80"/>
       <c r="N69" s="82"/>
       <c r="O69" s="83" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P69" s="83" t="s">
         <v>247</v>
       </c>
       <c r="Q69" s="84" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="R69" s="80"/>
       <c r="S69" s="80"/>
@@ -4899,13 +4890,13 @@
       <c r="M70" s="14"/>
       <c r="N70" s="33"/>
       <c r="O70" s="35" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P70" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q70" s="75" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="R70" s="14"/>
       <c r="S70" s="14"/>
@@ -4930,9 +4921,7 @@
       <c r="D71" s="36"/>
       <c r="E71" s="14"/>
       <c r="F71" s="14"/>
-      <c r="G71" s="37" t="s">
-        <v>229</v>
-      </c>
+      <c r="G71" s="37"/>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="38"/>
@@ -4941,13 +4930,13 @@
       <c r="M71" s="14"/>
       <c r="N71" s="33"/>
       <c r="O71" s="35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P71" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q71" s="75" t="s">
-        <v>262</v>
+        <v>258</v>
+      </c>
+      <c r="Q71" s="85" t="s">
+        <v>259</v>
       </c>
       <c r="R71" s="14"/>
       <c r="S71" s="14"/>
@@ -4983,13 +4972,13 @@
       <c r="M72" s="14"/>
       <c r="N72" s="33"/>
       <c r="O72" s="35" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P72" s="35" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q72" s="75" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="R72" s="14"/>
       <c r="S72" s="14"/>
@@ -5025,13 +5014,13 @@
       <c r="M73" s="14"/>
       <c r="N73" s="33"/>
       <c r="O73" s="35" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P73" s="35" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="Q73" s="75" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R73" s="14"/>
       <c r="S73" s="14"/>
@@ -5067,13 +5056,13 @@
       <c r="M74" s="14"/>
       <c r="N74" s="33"/>
       <c r="O74" s="35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P74" s="35" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="Q74" s="75" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R74" s="14"/>
       <c r="S74" s="14"/>
@@ -5109,13 +5098,13 @@
       <c r="M75" s="14"/>
       <c r="N75" s="33"/>
       <c r="O75" s="35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P75" s="35" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="Q75" s="75" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="R75" s="14"/>
       <c r="S75" s="14"/>
@@ -5151,13 +5140,13 @@
       <c r="M76" s="14"/>
       <c r="N76" s="33"/>
       <c r="O76" s="35" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P76" s="35" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="75" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R76" s="14"/>
       <c r="S76" s="14"/>
@@ -5193,13 +5182,13 @@
       <c r="M77" s="14"/>
       <c r="N77" s="33"/>
       <c r="O77" s="35" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="P77" s="35" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="Q77" s="75" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="14"/>
@@ -5235,13 +5224,13 @@
       <c r="M78" s="14"/>
       <c r="N78" s="33"/>
       <c r="O78" s="35" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P78" s="35" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="Q78" s="75" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="R78" s="14"/>
       <c r="S78" s="14"/>
@@ -5277,13 +5266,13 @@
       <c r="M79" s="14"/>
       <c r="N79" s="33"/>
       <c r="O79" s="35" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="P79" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R79" s="14"/>
       <c r="S79" s="14"/>
@@ -5319,13 +5308,13 @@
       <c r="M80" s="14"/>
       <c r="N80" s="33"/>
       <c r="O80" s="35" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="P80" s="35" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="Q80" s="75" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R80" s="14"/>
       <c r="S80" s="14"/>
@@ -5340,13 +5329,19 @@
       <c r="AB80" s="14"/>
     </row>
     <row r="81">
-      <c r="A81" s="38"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
+      <c r="A81" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" s="74" t="s">
+        <v>223</v>
+      </c>
+      <c r="C81" s="74"/>
       <c r="D81" s="36"/>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
-      <c r="G81" s="38"/>
+      <c r="G81" s="37" t="s">
+        <v>229</v>
+      </c>
       <c r="H81" s="14"/>
       <c r="I81" s="14"/>
       <c r="J81" s="38"/>
@@ -5354,9 +5349,15 @@
       <c r="L81" s="14"/>
       <c r="M81" s="14"/>
       <c r="N81" s="33"/>
-      <c r="O81" s="14"/>
-      <c r="P81" s="14"/>
-      <c r="Q81" s="14"/>
+      <c r="O81" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="P81" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q81" s="75" t="s">
+        <v>281</v>
+      </c>
       <c r="R81" s="14"/>
       <c r="S81" s="14"/>
       <c r="T81" s="14"/>
@@ -5370,117 +5371,105 @@
       <c r="AB81" s="14"/>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="38"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
+      <c r="N82" s="33"/>
+      <c r="O82" s="14"/>
+      <c r="P82" s="14"/>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="14"/>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="14"/>
+      <c r="Z82" s="14"/>
+      <c r="AA82" s="14"/>
+      <c r="AB82" s="14"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="B82" s="30"/>
-      <c r="C82" s="85" t="s">
+      <c r="B83" s="30"/>
+      <c r="C83" s="86" t="s">
         <v>283</v>
       </c>
-      <c r="D82" s="31"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="30"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="30"/>
-      <c r="L82" s="30"/>
-      <c r="M82" s="30"/>
-      <c r="N82" s="33"/>
-      <c r="O82" s="30"/>
-      <c r="P82" s="30"/>
-      <c r="Q82" s="30"/>
-      <c r="R82" s="30"/>
-      <c r="S82" s="30"/>
-      <c r="T82" s="30"/>
-      <c r="U82" s="30"/>
-      <c r="V82" s="30"/>
-      <c r="W82" s="30"/>
-      <c r="X82" s="30"/>
-      <c r="Y82" s="30"/>
-      <c r="Z82" s="30"/>
-      <c r="AA82" s="30"/>
-      <c r="AB82" s="30"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B83" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="C83" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="D83" s="36"/>
-      <c r="E83" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="F83" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
       <c r="N83" s="33"/>
-      <c r="O83" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="P83" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q83" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="R83" s="14"/>
-      <c r="S83" s="14"/>
-      <c r="T83" s="14"/>
-      <c r="U83" s="14"/>
-      <c r="V83" s="14"/>
-      <c r="W83" s="14"/>
-      <c r="X83" s="14"/>
-      <c r="Y83" s="14"/>
-      <c r="Z83" s="14"/>
-      <c r="AA83" s="14"/>
-      <c r="AB83" s="14"/>
+      <c r="O83" s="30"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="30"/>
+      <c r="R83" s="30"/>
+      <c r="S83" s="30"/>
+      <c r="T83" s="30"/>
+      <c r="U83" s="30"/>
+      <c r="V83" s="30"/>
+      <c r="W83" s="30"/>
+      <c r="X83" s="30"/>
+      <c r="Y83" s="30"/>
+      <c r="Z83" s="30"/>
+      <c r="AA83" s="30"/>
+      <c r="AB83" s="30"/>
     </row>
     <row r="84">
       <c r="A84" s="37" t="s">
         <v>80</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="C84" s="35"/>
+        <v>284</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>285</v>
+      </c>
       <c r="D84" s="36"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
+      <c r="E84" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>72</v>
+      </c>
       <c r="G84" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="L84" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="M84" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="N84" s="54"/>
-      <c r="O84" s="35"/>
-      <c r="P84" s="35"/>
-      <c r="Q84" s="35"/>
+        <v>286</v>
+      </c>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
+      <c r="N84" s="33"/>
+      <c r="O84" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="P84" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q84" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="R84" s="14"/>
       <c r="S84" s="14"/>
       <c r="T84" s="14"/>
@@ -5498,25 +5487,31 @@
         <v>80</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="C85" s="14"/>
+        <v>288</v>
+      </c>
+      <c r="C85" s="35"/>
       <c r="D85" s="36"/>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
       <c r="G85" s="37" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H85" s="14"/>
       <c r="I85" s="14"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="33"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14"/>
-      <c r="Q85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="L85" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="M85" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="N85" s="54"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+      <c r="Q85" s="35"/>
       <c r="R85" s="14"/>
       <c r="S85" s="14"/>
       <c r="T85" s="14"/>
@@ -5534,14 +5529,14 @@
         <v>80</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="36"/>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
       <c r="G86" s="37" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
@@ -5570,12 +5565,12 @@
         <v>80</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="36"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
       <c r="G87" s="37" t="s">
         <v>294</v>
       </c>
@@ -5606,7 +5601,7 @@
         <v>80</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="36"/>
@@ -5642,7 +5637,7 @@
         <v>80</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="36"/>
@@ -5678,7 +5673,7 @@
         <v>80</v>
       </c>
       <c r="B90" s="35" t="s">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="36"/>
@@ -5710,13 +5705,19 @@
       <c r="AB90" s="14"/>
     </row>
     <row r="91">
-      <c r="A91" s="38"/>
-      <c r="B91" s="14"/>
+      <c r="A91" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B91" s="35" t="s">
+        <v>119</v>
+      </c>
       <c r="C91" s="14"/>
       <c r="D91" s="36"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="38"/>
+      <c r="E91" s="35"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="37" t="s">
+        <v>294</v>
+      </c>
       <c r="H91" s="14"/>
       <c r="I91" s="14"/>
       <c r="J91" s="38"/>
@@ -34299,9 +34300,39 @@
       <c r="AA1043" s="14"/>
       <c r="AB1043" s="14"/>
     </row>
+    <row r="1044">
+      <c r="A1044" s="38"/>
+      <c r="B1044" s="14"/>
+      <c r="C1044" s="14"/>
+      <c r="D1044" s="36"/>
+      <c r="E1044" s="14"/>
+      <c r="F1044" s="14"/>
+      <c r="G1044" s="38"/>
+      <c r="H1044" s="14"/>
+      <c r="I1044" s="14"/>
+      <c r="J1044" s="38"/>
+      <c r="K1044" s="14"/>
+      <c r="L1044" s="14"/>
+      <c r="M1044" s="14"/>
+      <c r="N1044" s="33"/>
+      <c r="O1044" s="14"/>
+      <c r="P1044" s="14"/>
+      <c r="Q1044" s="14"/>
+      <c r="R1044" s="14"/>
+      <c r="S1044" s="14"/>
+      <c r="T1044" s="14"/>
+      <c r="U1044" s="14"/>
+      <c r="V1044" s="14"/>
+      <c r="W1044" s="14"/>
+      <c r="X1044" s="14"/>
+      <c r="Y1044" s="14"/>
+      <c r="Z1044" s="14"/>
+      <c r="AA1044" s="14"/>
+      <c r="AB1044" s="14"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A65:B65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId4" ref="F1"/>
@@ -34314,10 +34345,10 @@
     <hyperlink r:id="rId11" ref="K2"/>
     <hyperlink r:id="rId12" ref="O2"/>
     <hyperlink r:id="rId13" ref="A4"/>
-    <hyperlink r:id="rId14" ref="G39"/>
-    <hyperlink r:id="rId15" ref="C43"/>
-    <hyperlink r:id="rId16" location="_cols_show=nonempty" ref="G54"/>
-    <hyperlink r:id="rId17" ref="C82"/>
+    <hyperlink r:id="rId14" ref="G40"/>
+    <hyperlink r:id="rId15" ref="C44"/>
+    <hyperlink r:id="rId16" location="_cols_show=nonempty" ref="G55"/>
+    <hyperlink r:id="rId17" ref="C83"/>
   </hyperlinks>
   <drawing r:id="rId18"/>
   <legacyDrawing r:id="rId19"/>
@@ -34382,38 +34413,38 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -34467,27 +34498,27 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
